--- a/MSME/Tranch calcualtions.xlsx
+++ b/MSME/Tranch calcualtions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="3"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="113">
   <si>
     <t>CGPAN</t>
   </si>
@@ -336,9 +336,6 @@
   </si>
   <si>
     <t>Net Loan Amount (D1)</t>
-  </si>
-  <si>
-    <t>30-03-2026</t>
   </si>
   <si>
     <t>D1-C</t>
@@ -1084,12 +1081,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -2247,58 +2245,58 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" s="17" customFormat="1" spans="1:9">
-      <c r="A2" s="17" t="s">
+    <row r="2" s="18" customFormat="1" spans="1:9">
+      <c r="A2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="18">
         <v>10000</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="18">
         <v>500</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="19">
         <v>46179</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="20">
         <v>116.73</v>
       </c>
-      <c r="G2" s="17">
-        <v>0</v>
-      </c>
-      <c r="H2" s="17">
+      <c r="G2" s="18">
+        <v>0</v>
+      </c>
+      <c r="H2" s="18">
         <v>10.51</v>
       </c>
-      <c r="I2" s="17">
+      <c r="I2" s="18">
         <v>10.51</v>
       </c>
     </row>
-    <row r="3" s="17" customFormat="1" spans="1:9">
-      <c r="A3" s="17" t="s">
+    <row r="3" s="18" customFormat="1" spans="1:9">
+      <c r="A3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="18">
         <v>116.73</v>
       </c>
-      <c r="G3" s="17">
-        <v>0</v>
-      </c>
-      <c r="H3" s="17">
+      <c r="G3" s="18">
+        <v>0</v>
+      </c>
+      <c r="H3" s="18">
         <v>10.51</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="18">
         <v>10.51</v>
       </c>
     </row>
@@ -2341,7 +2339,7 @@
       <c r="E5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="20">
         <v>38.78</v>
       </c>
       <c r="G5">
@@ -2355,25 +2353,25 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <f>SUM(F2:F5)</f>
         <v>311.02</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="21">
         <f>SUM(G2:G5)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <f>SUM(H2:H5)</f>
         <v>28</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="21">
         <f>SUM(I2:I5)</f>
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="26" t="s">
         <v>19</v>
       </c>
       <c r="D8">
@@ -2382,12 +2380,12 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="F12" s="15">
+      <c r="F12" s="16">
         <v>46179</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="F13" s="15">
+      <c r="F13" s="16">
         <v>46477</v>
       </c>
     </row>
@@ -2396,95 +2394,95 @@
         <f>F13-F12+1</f>
         <v>299</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="H14" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="24">
         <f>C2-500</f>
         <v>9500</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="G15" s="22"/>
-      <c r="H15" s="23" t="s">
+      <c r="G15" s="23"/>
+      <c r="H15" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="24">
         <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="G16" s="22"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
     </row>
     <row r="17" spans="7:9">
-      <c r="G17" s="22"/>
-      <c r="H17" s="23" t="s">
+      <c r="G17" s="23"/>
+      <c r="H17" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="25">
         <f>ROUND(I14*1.5%*(I15/365),2)</f>
         <v>116.73</v>
       </c>
     </row>
     <row r="18" spans="7:9">
-      <c r="G18" s="22"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
     </row>
     <row r="19" spans="7:9">
-      <c r="G19" s="22"/>
-      <c r="H19" s="23" t="s">
+      <c r="G19" s="23"/>
+      <c r="H19" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="23"/>
+      <c r="I19" s="24"/>
     </row>
     <row r="20" spans="7:9">
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
     </row>
     <row r="21" spans="7:9">
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" spans="7:9">
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" spans="7:9">
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="23" t="s">
+      <c r="H23" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="24">
         <f>C4-500</f>
         <v>9500</v>
       </c>
     </row>
     <row r="24" spans="7:9">
-      <c r="G24" s="22"/>
-      <c r="H24" s="23" t="s">
+      <c r="G24" s="23"/>
+      <c r="H24" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="24">
         <v>299</v>
       </c>
     </row>
     <row r="25" spans="7:9">
-      <c r="G25" s="22"/>
-      <c r="H25" s="23" t="s">
+      <c r="G25" s="23"/>
+      <c r="H25" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="25">
         <f>(I23*0.5%*(I24/365))</f>
         <v>38.9109589041096</v>
       </c>
@@ -2550,16 +2548,16 @@
       <c r="H1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="11" t="s">
         <v>31</v>
       </c>
       <c r="N1" t="s">
@@ -2594,16 +2592,16 @@
       <c r="H2">
         <v>11.61</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="12">
         <v>10000</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="15">
         <v>500</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="11">
         <v>299</v>
       </c>
       <c r="N2">
@@ -2640,16 +2638,16 @@
       <c r="H3">
         <v>11.61</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="12">
         <v>10000</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="15">
         <v>500</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="11">
         <v>299</v>
       </c>
       <c r="N3">
@@ -2686,16 +2684,16 @@
       <c r="H4">
         <v>3.87</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="12">
         <v>10000</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="15">
         <v>500</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="11">
         <v>299</v>
       </c>
       <c r="N4">
@@ -2732,16 +2730,16 @@
       <c r="H5">
         <v>3.87</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="12">
         <v>10000</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="15">
         <v>500</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="11">
         <v>299</v>
       </c>
       <c r="N5">
@@ -2760,12 +2758,12 @@
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:16">
-      <c r="G15" s="15">
+      <c r="G15" s="16">
         <v>46179</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:16">
-      <c r="G16" s="15">
+      <c r="G16" s="16">
         <v>46477</v>
       </c>
     </row>
@@ -2827,19 +2825,19 @@
       <c r="H1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="11" t="s">
         <v>31</v>
       </c>
       <c r="O1" t="s">
@@ -2874,19 +2872,19 @@
       <c r="H2">
         <v>0.1</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="12">
         <v>10000</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="13">
         <v>1000</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="14">
         <v>100</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="15">
         <v>500</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="11">
         <v>269</v>
       </c>
       <c r="O2">
@@ -2923,19 +2921,19 @@
       <c r="H3">
         <v>0.1</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="12">
         <v>10000</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="13">
         <v>1000</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="14">
         <v>100</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="15">
         <v>500</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="11">
         <v>269</v>
       </c>
       <c r="O3">
@@ -2972,19 +2970,19 @@
       <c r="H4">
         <v>0.03</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="12">
         <v>10000</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="13">
         <v>1000</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="14">
         <v>100</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="15">
         <v>500</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="11">
         <v>269</v>
       </c>
       <c r="O4">
@@ -3021,19 +3019,19 @@
       <c r="H5">
         <v>0.03</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="12">
         <v>10000</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="13">
         <v>1000</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="14">
         <v>100</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="15">
         <v>500</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="11">
         <v>269</v>
       </c>
       <c r="O5">
@@ -3070,12 +3068,12 @@
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="J15" s="15">
+      <c r="J15" s="16">
         <v>46209</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="J16" s="15">
+      <c r="J16" s="16">
         <v>46477</v>
       </c>
       <c r="L16">
@@ -3119,6 +3117,7 @@
     <col min="13" max="13" width="20.5714285714286" customWidth="1"/>
     <col min="14" max="14" width="44.5714285714286" customWidth="1"/>
     <col min="16" max="16" width="14.5714285714286" customWidth="1"/>
+    <col min="17" max="17" width="16.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:35">
@@ -3278,7 +3277,7 @@
         <v>10000000.79</v>
       </c>
       <c r="Q2" s="2">
-        <v>45748</v>
+        <v>46199</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>86</v>
@@ -3385,7 +3384,7 @@
         <v>10000000.02</v>
       </c>
       <c r="Q3" s="2">
-        <v>45748</v>
+        <v>46199</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>86</v>
@@ -3492,7 +3491,7 @@
         <v>2000000.33</v>
       </c>
       <c r="Q4" s="2">
-        <v>45748</v>
+        <v>46199</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>86</v>
@@ -3599,7 +3598,7 @@
         <v>2000000.65</v>
       </c>
       <c r="Q5" s="2">
-        <v>45748</v>
+        <v>46199</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>86</v>
@@ -3703,30 +3702,30 @@
       <c r="C12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5">
+        <v>46111</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L12" s="6">
+      <c r="L12" s="7">
         <f>C12-Z2</f>
         <v>9500</v>
       </c>
-      <c r="N12" s="7" t="s">
-        <v>104</v>
+      <c r="N12" s="8" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:35">
@@ -3740,7 +3739,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -3751,10 +3750,10 @@
       <c r="G13" s="4">
         <v>0</v>
       </c>
-      <c r="H13" s="5">
-        <v>0</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7">
         <f>C13-Z3</f>
         <v>9500</v>
       </c>
@@ -3762,7 +3761,7 @@
         <v>46179</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:35">
@@ -3776,7 +3775,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -3787,10 +3786,10 @@
       <c r="G14" s="4">
         <v>0</v>
       </c>
-      <c r="H14" s="5">
-        <v>0</v>
-      </c>
-      <c r="L14" s="6">
+      <c r="H14" s="6">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
         <f>C14-Z4</f>
         <v>9500</v>
       </c>
@@ -3798,7 +3797,7 @@
         <v>46477</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:35">
@@ -3812,7 +3811,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -3823,10 +3822,10 @@
       <c r="G15" s="4">
         <v>0</v>
       </c>
-      <c r="H15" s="5">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6">
+      <c r="H15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
         <f>C15-Z5</f>
         <v>9500</v>
       </c>
@@ -3836,7 +3835,7 @@
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:35">
-      <c r="L16" s="8"/>
+      <c r="L16" s="9"/>
     </row>
     <row r="17" s="1" customFormat="1"/>
     <row r="18" s="1" customFormat="1"/>
@@ -3871,13 +3870,13 @@
         <v>100</v>
       </c>
       <c r="L21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="N21" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:14">
@@ -3906,9 +3905,9 @@
         <v>11.61</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="6">
+        <v>110</v>
+      </c>
+      <c r="L22" s="7">
         <f>C12+C22-Z2</f>
         <v>10500</v>
       </c>
@@ -3946,7 +3945,7 @@
       <c r="H23" s="1">
         <v>11.61</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="7">
         <f>C13+C23-Z3</f>
         <v>10500</v>
       </c>
@@ -3984,7 +3983,7 @@
       <c r="H24" s="1">
         <v>3.87</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="7">
         <f>C14+C24-Z4</f>
         <v>10500</v>
       </c>
@@ -4022,7 +4021,7 @@
       <c r="H25" s="1">
         <v>3.87</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="7">
         <f>C15+C25-Z5</f>
         <v>10500</v>
       </c>
@@ -4070,10 +4069,10 @@
         <v>100</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="N29" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="45" spans="1:14">
@@ -4101,8 +4100,8 @@
       <c r="H30" s="1">
         <v>0.1</v>
       </c>
-      <c r="K30" s="9" t="s">
-        <v>113</v>
+      <c r="K30" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="L30" s="1">
         <f>N30*1.5%*269/365</f>
@@ -4219,7 +4218,7 @@
     <row r="35" s="1" customFormat="1"/>
     <row r="36" s="1" customFormat="1"/>
     <row r="37" s="1" customFormat="1" spans="1:14">
-      <c r="N37" s="6"/>
+      <c r="N37" s="7"/>
     </row>
     <row r="38" s="1" customFormat="1"/>
   </sheetData>
